--- a/exemple-arborescence-modele-vide.xlsx
+++ b/exemple-arborescence-modele-vide.xlsx
@@ -305,7 +305,7 @@
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>Code d'un enjeu (ex : E1) OU d'un indicateur (ex : I1). (obligatoire)</t>
+        <t>Code d'un enjeu (ex : E1). (obligatoire)</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -330,7 +330,7 @@
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>Code d'un enjeu (ex : E1) OU d'un indicateur (ex : I1). (obligatoire)</t>
+        <t>Code d'un enjeu (ex : E1). (obligatoire)</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -1193,14 +1193,14 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Espèces (TaxRef) rattachées à un enjeu ou à un indicateur, via le code de la cible.</t>
+          <t>Espèces (TaxRef) rattachées à un enjeu, via le code de la cible.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>cible (enjeu ou indicateur)</t>
+          <t>cible (enjeu)</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -1256,14 +1256,14 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Habitats (HabRef) rattachés à un enjeu ou à un indicateur, via le code de la cible.</t>
+          <t>Habitats (HabRef) rattachés à un enjeu, via le code de la cible.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>cible (enjeu ou indicateur)</t>
+          <t>cible (enjeu)</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
